--- a/backend/backups/category11_pet_services_FINAL.xlsx
+++ b/backend/backups/category11_pet_services_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,815 +425,888 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4f744793-3e3c-532a-bc2e-40330d326e13</t>
+          <t>5c61d5df-f335-5c43-b47f-d671b134142c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dog Grooming Service Variation 1</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Dog Grooming</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dog Grooming</t>
+          <t>Dog Grooming Premium Care Option 1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>700</v>
+        <v>2099</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Dog Grooming service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Dog Grooming Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog grooming service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Grooming specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dog Grooming Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.577149+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.577149+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Grooming Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09d1eee1-5656-5d4b-af72-69fc9e8bea2b</t>
+          <t>a407e5eb-c8eb-5981-9caa-78da15b6ae97</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dog Grooming Service Variation 2</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Dog Grooming</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dog Grooming</t>
+          <t>Dog Grooming Premium Care Option 8</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>900</v>
+        <v>2799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Dog Grooming service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Dog Grooming Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog grooming service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Grooming specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dog Grooming Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.580890+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.580890+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Grooming Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a407e5eb-c8eb-5981-9caa-78da15b6ae97</t>
+          <t>b9adf640-88d1-5fe3-966a-d530e6c0c105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dog Grooming Service Variation 3</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Dog Training</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dog Grooming</t>
+          <t>Dog Training Premium Care Option 11</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1100</v>
+        <v>3099</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Dog Training Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog grooming service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Grooming specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dog Training Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.583614+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.583614+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>047f1a2c-5560-5290-ad70-932d31819b3d</t>
+          <t>65a78a43-3868-54d2-a616-642dbf2bdea2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dog Grooming Service Variation 4</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Dog Training</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dog Grooming</t>
+          <t>Dog Training Premium Care Option 2</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1300</v>
+        <v>2199</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Dog Training Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog grooming service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Grooming specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dog Training Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.586108+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.586108+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5c61d5df-f335-5c43-b47f-d671b134142c</t>
+          <t>8d5b166d-d416-574b-813e-2ded0a26c4e3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dog Grooming Service Variation 5</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Dog Training</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dog Grooming</t>
+          <t>Dog Training Premium Care Option 4</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1500</v>
+        <v>2399</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Dog Training Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog grooming service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Grooming specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dog Training Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.588309+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.588309+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3cb848a2-cbd6-5efb-9cb8-9ca7fbd33ac9</t>
+          <t>aabd7a83-ae18-582b-914d-91e31cdfc9bf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dog Grooming Service Variation 6</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Dog Training</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dog Grooming</t>
+          <t>Dog Training Premium Care Option 9</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1700</v>
+        <v>2899</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Dog Training Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog grooming service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Grooming specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dog Training Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.590778+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.590778+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aabd7a83-ae18-582b-914d-91e31cdfc9bf</t>
+          <t>d7dd1acb-f1ab-5012-bc08-727af3409adf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dog Training Service Variation 1</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Accessories &amp; Nutrition</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dog Training</t>
+          <t>Pet Accessories &amp; Nutrition Premium Care Option 12</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>700</v>
+        <v>3199</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Pet Accessories &amp; Nutrition service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Pet Accessories &amp; Nutrition Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog training service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Training specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Accessories &amp; Nutrition Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.593242+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.593242+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Accessories &amp; Nutrition Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8d5b166d-d416-574b-813e-2ded0a26c4e3</t>
+          <t>6a9b539a-9be2-5e2c-8f91-e43cc588141c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dog Training Service Variation 2</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Accessories &amp; Nutrition</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dog Training</t>
+          <t>Pet Accessories &amp; Nutrition Premium Care Option 3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>900</v>
+        <v>2299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Pet Accessories &amp; Nutrition service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Pet Accessories &amp; Nutrition Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog training service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Training specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Accessories &amp; Nutrition Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.595837+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.595837+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Accessories &amp; Nutrition Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>65a78a43-3868-54d2-a616-642dbf2bdea2</t>
+          <t>90e91453-4a3d-5cea-be1e-9aa3eae3b5b2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dog Training Service Variation 3</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Accessories &amp; Nutrition</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dog Training</t>
+          <t>Pet Accessories &amp; Nutrition Premium Care Option 5</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1100</v>
+        <v>2499</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Pet Accessories &amp; Nutrition service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Pet Accessories &amp; Nutrition Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog training service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Training specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Accessories &amp; Nutrition Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.598304+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.598304+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Accessories &amp; Nutrition Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b9adf640-88d1-5fe3-966a-d530e6c0c105</t>
+          <t>23944650-654e-5f8a-bc57-57dc6985c98f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dog Training Service Variation 4</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Care</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dog Training</t>
+          <t>Dog Walking &amp; Exercise Visit (30 Mins)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1300</v>
+        <v>299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Background-verified pet lover taking your dog for brisk outdoor walk, potty break, and hydration.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Dog Walking &amp; Exercise Visit (30 Mins) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog training service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Training specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dog Walking &amp; Exercise Visit (30 Mins) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.600577+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.600577+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Dog Walking &amp; Exercise Visit (30 Mins) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4dbbb340-3245-5037-8b45-c60227dab7d3</t>
+          <t>3cb848a2-cbd6-5efb-9cb8-9ca7fbd33ac9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dog Training Service Variation 5</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Care</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dog Training</t>
+          <t>In-Home Pet Sitting &amp; Feeding (Per Visit)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1500</v>
+        <v>499</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Caring pet sitter visiting home to feed food, clean litter box, give medication, and play with pets.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional In-Home Pet Sitting &amp; Feeding (Per Visit) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Professional dog training service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Dog Training specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete In-Home Pet Sitting &amp; Feeding (Per Visit) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.602618+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.602618+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does In-Home Pet Sitting &amp; Feeding (Per Visit) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6a9b539a-9be2-5e2c-8f91-e43cc588141c</t>
+          <t>09d1eee1-5656-5d4b-af72-69fc9e8bea2b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition Service Variation 1</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Grooming</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition</t>
+          <t>Cat Bath, Fur De-Shedding &amp; Nail Trim</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>700</v>
+        <v>1299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Gentle low-stress waterless or warm water cat bath, coat brushing, and claw trimming.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Cat Bath, Fur De-Shedding &amp; Nail Trim procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet accessories &amp; nutrition service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Accessories &amp; Nutrition specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Cat Bath, Fur De-Shedding &amp; Nail Trim procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.605122+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.605122+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Cat Bath, Fur De-Shedding &amp; Nail Trim take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>d7dd1acb-f1ab-5012-bc08-727af3409adf</t>
+          <t>047f1a2c-5560-5290-ad70-932d31819b3d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition Service Variation 2</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Grooming</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition</t>
+          <t>Full Dog Grooming &amp; Haircut Spa Package</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>1499</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Warm bath, breed-specific style haircut, nail clipping, ear cleaning, and anti-tick shampoo bath.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Full Dog Grooming &amp; Haircut Spa Package procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet accessories &amp; nutrition service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Accessories &amp; Nutrition specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Full Dog Grooming &amp; Haircut Spa Package procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.607326+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.607326+00:00</t>
+          <t>[{'answer': 'The session typically takes around 75 minutes.', 'question': 'How long does Full Dog Grooming &amp; Haircut Spa Package take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23944650-654e-5f8a-bc57-57dc6985c98f</t>
+          <t>4dbbb340-3245-5037-8b45-c60227dab7d3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition Service Variation 3</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Grooming</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition</t>
+          <t>Medicated Anti-Tick &amp; Flea Bath Treatment</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1100</v>
+        <v>899</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Medicated dip shampoo eliminating ticks, fleas, and mites followed by thorough blow-dry.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Medicated Anti-Tick &amp; Flea Bath Treatment procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet accessories &amp; nutrition service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Accessories &amp; Nutrition specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Medicated Anti-Tick &amp; Flea Bath Treatment procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.609731+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.609731+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Medicated Anti-Tick &amp; Flea Bath Treatment take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>90e91453-4a3d-5cea-be1e-9aa3eae3b5b2</t>
+          <t>4f744793-3e3c-532a-bc2e-40330d326e13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition Service Variation 4</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Grooming</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition</t>
+          <t>Pet Ear Cleaning &amp; Hygiene Sanitize Pack</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1300</v>
+        <v>399</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Clearing ear wax, paw pad trimming, sanitary area trim, and mouth freshener spray.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Pet Ear Cleaning &amp; Hygiene Sanitize Pack procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet accessories &amp; nutrition service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Accessories &amp; Nutrition specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Ear Cleaning &amp; Hygiene Sanitize Pack procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.613105+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.613105+00:00</t>
+          <t>[{'answer': 'The session typically takes around 25 minutes.', 'question': 'How long does Pet Ear Cleaning &amp; Hygiene Sanitize Pack take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1262,495 +1318,545 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Service Variation 1</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Sitting &amp; Boarding</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding</t>
+          <t>Pet Sitting &amp; Boarding Premium Care Option 10</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>700</v>
+        <v>2999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Pet Sitting &amp; Boarding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Pet Sitting &amp; Boarding Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet sitting &amp; boarding service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Sitting &amp; Boarding specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Sitting &amp; Boarding Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.615500+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.615500+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Sitting &amp; Boarding Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>97919a8d-c4a8-5850-91e5-fd8a99a04845</t>
+          <t>f519aa47-1674-5bb3-8598-72dd04debe25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Service Variation 2</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Sitting &amp; Boarding</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding</t>
+          <t>Pet Sitting &amp; Boarding Premium Care Option 16</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>900</v>
+        <v>3599</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Pet Sitting &amp; Boarding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Pet Sitting &amp; Boarding Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet sitting &amp; boarding service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Sitting &amp; Boarding specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Sitting &amp; Boarding Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.618260+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.618260+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Sitting &amp; Boarding Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49fa8ea4-458a-52ff-9280-25c9d4d3aa0f</t>
+          <t>97919a8d-c4a8-5850-91e5-fd8a99a04845</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Service Variation 3</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Sitting &amp; Boarding</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding</t>
+          <t>Pet Sitting &amp; Boarding Premium Care Option 6</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1100</v>
+        <v>2599</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Pet Sitting &amp; Boarding service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Pet Sitting &amp; Boarding Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet sitting &amp; boarding service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Sitting &amp; Boarding specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Sitting &amp; Boarding Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.620360+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.620360+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Sitting &amp; Boarding Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0fe13cb7-d511-5bae-aa14-7ea32861f650</t>
+          <t>49fa8ea4-458a-52ff-9280-25c9d4d3aa0f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Service Variation 4</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Pet Training</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding</t>
+          <t>Obedience &amp; Puppy Basic Behavioral Training</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1300</v>
+        <v>4999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>10-session trainer teaching Sit, Stay, Heel, Leash walking, and stopping unwanted biting/chewing.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Obedience &amp; Puppy Basic Behavioral Training procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet sitting &amp; boarding service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Sitting &amp; Boarding specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Obedience &amp; Puppy Basic Behavioral Training procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.623038+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.623038+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Obedience &amp; Puppy Basic Behavioral Training take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f519aa47-1674-5bb3-8598-72dd04debe25</t>
+          <t>0fe13cb7-d511-5bae-aa14-7ea32861f650</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Service Variation 5</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Veterinary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding</t>
+          <t>At-Home Veterinary Health Checkup &amp; Vaccination</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1500</v>
+        <v>799</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Licensed vet visiting home for routine health exam, Deworming, and Annual 7-in-1 / Rabies vaccine.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional At-Home Veterinary Health Checkup &amp; Vaccination procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Professional pet sitting &amp; boarding service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Pet Sitting &amp; Boarding specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete At-Home Veterinary Health Checkup &amp; Vaccination procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.625226+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.625226+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does At-Home Veterinary Health Checkup &amp; Vaccination take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f3d2721a-1c3a-5d38-8d5a-43b87fe3941f</t>
+          <t>e4c46c13-deb4-5980-8f9d-6a7beb40e017</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Service Variation 1</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Veterinary &amp; Health Checkup</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup</t>
+          <t>Veterinary &amp; Health Checkup Premium Care Option 13</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>700</v>
+        <v>3299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Professional veterinary &amp; health checkup service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Veterinary &amp; Health Checkup specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.628033+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.628033+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fcb9f5bb-5148-54f9-a41c-b54a97ac1a6c</t>
+          <t>e9ba5e71-3b0d-53e9-bda9-ace253bc0172</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Service Variation 2</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Veterinary &amp; Health Checkup</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup</t>
+          <t>Veterinary &amp; Health Checkup Premium Care Option 14</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>900</v>
+        <v>3399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Professional veterinary &amp; health checkup service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Veterinary &amp; Health Checkup specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.630523+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.630523+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>e4c46c13-deb4-5980-8f9d-6a7beb40e017</t>
+          <t>f3d2721a-1c3a-5d38-8d5a-43b87fe3941f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Service Variation 3</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Veterinary &amp; Health Checkup</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup</t>
+          <t>Veterinary &amp; Health Checkup Premium Care Option 15</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1100</v>
+        <v>3499</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Professional veterinary &amp; health checkup service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Veterinary &amp; Health Checkup specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.632877+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.632877+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9b26c969-6e22-51e2-9334-634b17229d5d</t>
+          <t>fcb9f5bb-5148-54f9-a41c-b54a97ac1a6c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Service Variation 4</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Veterinary &amp; Health Checkup</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup</t>
+          <t>Veterinary &amp; Health Checkup Premium Care Option 17</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1300</v>
+        <v>3699</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Professional veterinary &amp; health checkup service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Veterinary &amp; Health Checkup specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.634991+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.634991+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>e9ba5e71-3b0d-53e9-bda9-ace253bc0172</t>
+          <t>9b26c969-6e22-51e2-9334-634b17229d5d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Service Variation 5</t>
+          <t>11. Pet Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11. Pet Services</t>
+          <t>Veterinary &amp; Health Checkup</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup</t>
+          <t>Veterinary &amp; Health Checkup Premium Care Option 7</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1500</v>
+        <v>2699</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Initial pet assessment", "Service execution by certified pet professional", "Post-service health check", "Owner care tips"]</t>
+          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Professional veterinary &amp; health checkup service for the health and happiness of your pet.", "type": "description"}, {"type": "highlights", "items": ["Experienced Veterinary &amp; Health Checkup specialists", "Safe and stress-free environment", "Breed-specific care", "Owner briefing post-service"]}, {"type": "excluded_scope", "items": ["Cost of specialty grooming products", "Veterinary medication costs"]}, {"type": "process_steps", "steps": [{"title": "Pet Assessment", "description": "Evaluating the pet's breed, temperament, and specific needs", "step_number": 1}, {"title": "Service Preparation", "description": "Preparing equipment and a safe environment", "step_number": 2}, {"title": "Service Execution", "description": "Delivering the requested pet care service", "step_number": 3}, {"title": "Post-Service Check", "description": "Ensuring the pet is comfortable and healthy post-service", "step_number": 4}, {"title": "Owner Handover &amp; Tips", "description": "Briefing the owner on aftercare and next steps", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Monitor pet behaviour for 24 hours post-service", "Follow any dietary or medication advice given"]}, {"type": "tools_materials", "tools": ["Professional grooming kit", "Pet-safe cleaning products", "First-aid kit", "Leash and harness"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure pet has been fed at least 2 hours before grooming", "Provide vaccination records if applicable", "Keep a calm environment during the visit"]}, {"type": "expected_results", "items": "A clean, healthy, and happy pet with improved coat and behaviour."}, {"type": "important_notes", "items": "Aggressive pets may require additional handling precautions — please disclose temperament."}, {"type": "warranty", "details": "Free re-service if quality standards are not met on first visit.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, our professionals are trained to handle all dog and cat breeds.", "question": "Do you handle all breeds?"}, {"answer": "Absolutely — we only use vet-approved, non-toxic products.", "question": "Are the products pet-safe?"}, {"answer": "Yes, our groomers are trained in gentle handling for anxious animals.", "question": "Can you handle anxious pets?"}, {"answer": "Yes, we offer in-home mobile grooming services.", "question": "Do you offer mobile pet grooming?"}]}, {"type": "tips", "items": ["Regular grooming every 4-6 weeks keeps your pet's coat healthy."]}, {"dos": ["Share your pet's medical history with the professional before each visit."], "type": "dos_donts", "donts": ["Do not bathe your dog immediately before a grooming appointment."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.637083+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.637083+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>

--- a/backend/backups/category11_pet_services_FINAL.xlsx
+++ b/backend/backups/category11_pet_services_FINAL.xlsx
@@ -503,40 +503,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dog Grooming Premium Care Option 1</t>
+          <t>Deshedding &amp; Undercoat Fur Thinning Bath</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2099</v>
+        <v>1399</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Specialized high-end Dog Grooming service tailored to specific client needs with extended guarantee.</t>
+          <t>Specialized high-velocity blow dry and fur rake grooming removing loose dead undercoat hairs.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>['Professional Dog Grooming Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Deshedding &amp; Undercoat Fur Thinning Bath procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['Complete Dog Grooming Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Deshedding &amp; Undercoat Fur Thinning Bath procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Grooming Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Deshedding &amp; Undercoat Fur Thinning Bath take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -558,47 +558,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dog Grooming Premium Care Option 8</t>
+          <t>Pawdicure &amp; Organic Paw Balm Massage</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2799</v>
+        <v>399</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Specialized high-end Dog Grooming service tailored to specific client needs with extended guarantee.</t>
+          <t>Gentle nail clipping, paw pad hair trimming, and soothing organic beeswax balm massage.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>['Professional Dog Grooming Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Pawdicure &amp; Organic Paw Balm Massage procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>['Complete Dog Grooming Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Pawdicure &amp; Organic Paw Balm Massage procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Grooming Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 25 minutes.', 'question': 'How long does Pawdicure &amp; Organic Paw Balm Massage take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b9adf640-88d1-5fe3-966a-d530e6c0c105</t>
+          <t>aabd7a83-ae18-582b-914d-91e31cdfc9bf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -613,47 +613,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dog Training Premium Care Option 11</t>
+          <t>Advanced Trick &amp; Agility Training (5 Sessions)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3099</v>
+        <v>4999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
+          <t>Teaching high-five, roll over, weave poles, and fetch frisbee for mental stimulation.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>['Professional Dog Training Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Advanced Trick &amp; Agility Training (5 Sessions) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>['Complete Dog Training Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Advanced Trick &amp; Agility Training (5 Sessions) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Advanced Trick &amp; Agility Training (5 Sessions) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>65a78a43-3868-54d2-a616-642dbf2bdea2</t>
+          <t>b9adf640-88d1-5fe3-966a-d530e6c0c105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -668,40 +668,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dog Training Premium Care Option 2</t>
+          <t>Guard &amp; Watchdog Boundary Awareness Coaching</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2199</v>
+        <v>5499</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
+          <t>Teaching property perimeter alert barking on door knocks and stopping immediately on command.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>['Professional Dog Training Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Guard &amp; Watchdog Boundary Awareness Coaching procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>['Complete Dog Training Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Guard &amp; Watchdog Boundary Awareness Coaching procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Guard &amp; Watchdog Boundary Awareness Coaching take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -723,47 +723,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dog Training Premium Care Option 4</t>
+          <t>Leash Reactivity &amp; Outdoor Pulling Reset</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2399</v>
+        <v>3499</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
+          <t>Correction training for dogs that lunge, bark at other dogs, or pull excessively during walks.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>['Professional Dog Training Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Leash Reactivity &amp; Outdoor Pulling Reset procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>['Complete Dog Training Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Leash Reactivity &amp; Outdoor Pulling Reset procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Leash Reactivity &amp; Outdoor Pulling Reset take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aabd7a83-ae18-582b-914d-91e31cdfc9bf</t>
+          <t>65a78a43-3868-54d2-a616-642dbf2bdea2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -778,47 +778,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dog Training Premium Care Option 9</t>
+          <t>Puppy Potty &amp; Crate Training Intensive</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2899</v>
+        <v>3999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Specialized high-end Dog Training service tailored to specific client needs with extended guarantee.</t>
+          <t>Home consultation establishing a structured routine for indoor toilet habits and crate comfort.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>['Professional Dog Training Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Puppy Potty &amp; Crate Training Intensive procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>['Complete Dog Training Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Puppy Potty &amp; Crate Training Intensive procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Dog Training Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Puppy Potty &amp; Crate Training Intensive take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d7dd1acb-f1ab-5012-bc08-727af3409adf</t>
+          <t>6a9b539a-9be2-5e2c-8f91-e43cc588141c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,47 +833,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition Premium Care Option 12</t>
+          <t>Custom Raw &amp; Cooked Diet Meal Charting</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3199</v>
+        <v>1199</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Specialized high-end Pet Accessories &amp; Nutrition service tailored to specific client needs with extended guarantee.</t>
+          <t>Certified canine nutritionist planning breed-specific protein, calcium, and vitamin meal charts.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>['Professional Pet Accessories &amp; Nutrition Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Custom Raw &amp; Cooked Diet Meal Charting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>['Complete Pet Accessories &amp; Nutrition Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Custom Raw &amp; Cooked Diet Meal Charting procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Accessories &amp; Nutrition Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Custom Raw &amp; Cooked Diet Meal Charting take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6a9b539a-9be2-5e2c-8f91-e43cc588141c</t>
+          <t>90e91453-4a3d-5cea-be1e-9aa3eae3b5b2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -888,47 +888,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition Premium Care Option 3</t>
+          <t>Orthopedic Pet Bed &amp; Harness Fitment Consultation</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2299</v>
+        <v>499</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Specialized high-end Pet Accessories &amp; Nutrition service tailored to specific client needs with extended guarantee.</t>
+          <t>Measuring dog dimensions to prescribe anti-pull harnesses and joint-support orthopedic beds.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>['Professional Pet Accessories &amp; Nutrition Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Orthopedic Pet Bed &amp; Harness Fitment Consultation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>['Complete Pet Accessories &amp; Nutrition Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Orthopedic Pet Bed &amp; Harness Fitment Consultation procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Accessories &amp; Nutrition Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 30 minutes.', 'question': 'How long does Orthopedic Pet Bed &amp; Harness Fitment Consultation take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>90e91453-4a3d-5cea-be1e-9aa3eae3b5b2</t>
+          <t>d7dd1acb-f1ab-5012-bc08-727af3409adf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -943,40 +943,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pet Accessories &amp; Nutrition Premium Care Option 5</t>
+          <t>Pet Food Delivery &amp; Fresh Meat Subscription Setup</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2499</v>
+        <v>299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Specialized high-end Pet Accessories &amp; Nutrition service tailored to specific client needs with extended guarantee.</t>
+          <t>Arranging doorstep scheduled deliveries of fresh chicken broth, vegetables, and premium kibble.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>['Professional Pet Accessories &amp; Nutrition Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Pet Food Delivery &amp; Fresh Meat Subscription Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>['Complete Pet Accessories &amp; Nutrition Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Pet Food Delivery &amp; Fresh Meat Subscription Setup procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Accessories &amp; Nutrition Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 20 minutes.', 'question': 'How long does Pet Food Delivery &amp; Fresh Meat Subscription Setup take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>b196fd99-9ce8-53e9-83ca-da23d07b6320</t>
+          <t>97919a8d-c4a8-5850-91e5-fd8a99a04845</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,40 +1328,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Premium Care Option 10</t>
+          <t>Cage-Free Homestay Pet Boarding (Per Night)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2999</v>
+        <v>999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Specialized high-end Pet Sitting &amp; Boarding service tailored to specific client needs with extended guarantee.</t>
+          <t>Warm loving home environment with couch access, 3 daily walks, and live video check-in updates.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>['Professional Pet Sitting &amp; Boarding Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Cage-Free Homestay Pet Boarding (Per Night) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['Complete Pet Sitting &amp; Boarding Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Cage-Free Homestay Pet Boarding (Per Night) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Sitting &amp; Boarding Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 1440 minutes.', 'question': 'How long does Cage-Free Homestay Pet Boarding (Per Night) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1383,47 +1383,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Premium Care Option 16</t>
+          <t>Cat Sitting &amp; Litter Tray Maintenance Visit</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3599</v>
+        <v>399</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Specialized high-end Pet Sitting &amp; Boarding service tailored to specific client needs with extended guarantee.</t>
+          <t>In-home daily visit to scoop litter, refresh clean water fountain, and serve wet food.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>['Professional Pet Sitting &amp; Boarding Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Cat Sitting &amp; Litter Tray Maintenance Visit procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>['Complete Pet Sitting &amp; Boarding Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Cat Sitting &amp; Litter Tray Maintenance Visit procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Sitting &amp; Boarding Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 40 minutes.', 'question': 'How long does Cat Sitting &amp; Litter Tray Maintenance Visit take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>97919a8d-c4a8-5850-91e5-fd8a99a04845</t>
+          <t>b196fd99-9ce8-53e9-83ca-da23d07b6320</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1438,40 +1438,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pet Sitting &amp; Boarding Premium Care Option 6</t>
+          <t>Daycare Pet Playgroup &amp; Socialization</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2599</v>
+        <v>499</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Specialized high-end Pet Sitting &amp; Boarding service tailored to specific client needs with extended guarantee.</t>
+          <t>Supervised daytime group play in air-conditioned indoor pet play area with balls and agility tunnels.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>['Professional Pet Sitting &amp; Boarding Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Daycare Pet Playgroup &amp; Socialization procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>['Complete Pet Sitting &amp; Boarding Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Daycare Pet Playgroup &amp; Socialization procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Pet Sitting &amp; Boarding Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 360 minutes.', 'question': 'How long does Daycare Pet Playgroup &amp; Socialization take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>e4c46c13-deb4-5980-8f9d-6a7beb40e017</t>
+          <t>9b26c969-6e22-51e2-9334-634b17229d5d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1603,40 +1603,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Premium Care Option 13</t>
+          <t>Annual Anti-Rabies &amp; DHPPiL Booster Vaccine</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3299</v>
+        <v>899</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
+          <t>In-home administration of core annual vaccinations with official stamped medical booklet update.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Annual Anti-Rabies &amp; DHPPiL Booster Vaccine procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Annual Anti-Rabies &amp; DHPPiL Booster Vaccine procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 30 minutes.', 'question': 'How long does Annual Anti-Rabies &amp; DHPPiL Booster Vaccine take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1658,47 +1658,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Premium Care Option 14</t>
+          <t>Blood Sample Collection for CBC &amp; Kidney Profile</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3399</v>
+        <v>699</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
+          <t>Gentle doorstep blood draw sent to diagnostic lab with PDF report delivered within 24 hours.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Blood Sample Collection for CBC &amp; Kidney Profile procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Blood Sample Collection for CBC &amp; Kidney Profile procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 25 minutes.', 'question': 'How long does Blood Sample Collection for CBC &amp; Kidney Profile take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f3d2721a-1c3a-5d38-8d5a-43b87fe3941f</t>
+          <t>e4c46c13-deb4-5980-8f9d-6a7beb40e017</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1713,47 +1713,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Premium Care Option 15</t>
+          <t>Oral Dental Scaling &amp; Tartar Scraping</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3499</v>
+        <v>1499</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
+          <t>Painless ultrasonic dental cleaning removing yellow tartar buildup and stinky breath.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Oral Dental Scaling &amp; Tartar Scraping procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Oral Dental Scaling &amp; Tartar Scraping procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Oral Dental Scaling &amp; Tartar Scraping take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fcb9f5bb-5148-54f9-a41c-b54a97ac1a6c</t>
+          <t>f3d2721a-1c3a-5d38-8d5a-43b87fe3941f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1768,47 +1768,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Premium Care Option 17</t>
+          <t>Post-Surgery Wound Dressing &amp; Suture Removal</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3699</v>
+        <v>499</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
+          <t>Antiseptic cleaning of surgical stitches, fresh sterile bandage replacement, and recovery check.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Post-Surgery Wound Dressing &amp; Suture Removal procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Post-Surgery Wound Dressing &amp; Suture Removal procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 30 minutes.', 'question': 'How long does Post-Surgery Wound Dressing &amp; Suture Removal take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9b26c969-6e22-51e2-9334-634b17229d5d</t>
+          <t>fcb9f5bb-5148-54f9-a41c-b54a97ac1a6c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1823,40 +1823,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Veterinary &amp; Health Checkup Premium Care Option 7</t>
+          <t>Senior Pet Arthritis Joint Evaluation &amp; Pain Relief</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2699</v>
+        <v>899</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Specialized high-end Veterinary &amp; Health Checkup service tailored to specific client needs with extended guarantee.</t>
+          <t>Assessment of hip dysplasia, prescribing glucosamine supplements, and gentle mobility physical therapy.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>['Professional Veterinary &amp; Health Checkup Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Senior Pet Arthritis Joint Evaluation &amp; Pain Relief procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>['Complete Veterinary &amp; Health Checkup Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Senior Pet Arthritis Joint Evaluation &amp; Pain Relief procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Veterinary &amp; Health Checkup Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 40 minutes.', 'question': 'How long does Senior Pet Arthritis Joint Evaluation &amp; Pain Relief take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
